--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -35,7 +35,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -84,6 +84,12 @@
         <bgColor rgb="00FCE5CD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -111,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -141,6 +147,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2320,9 +2329,9 @@
           <t>"Você sabe qual é o seu perfil de vinho?" / "A gente te ajuda a descobrir."</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>Em produção</t>
         </is>
       </c>
     </row>
@@ -2342,9 +2351,9 @@
           <t>Perguntas rápidas, respondidas em 2 minutos. A gente entende o que você já bebe, o que gosta e o que ainda não experimentou.</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Em produção</t>
         </is>
       </c>
     </row>
@@ -2361,12 +2370,12 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>O resultado vem com o Mapa do Vinho: um guia com o seu perfil e sugestões pensadas pra você. Numa linguagem simples, sem forçar a venda.</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+          <t>O resultado vem com esse guia: seu perfil e sugestões pensadas pra você. Numa linguagem simples, sem forçar a venda.</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Em produção</t>
         </is>
       </c>
     </row>
@@ -2386,9 +2395,9 @@
           <t>A partir daí, toda sugestão que você recebe da comnéctar já é pensada pro seu perfil. Chega de indicação genérica.</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Em produção</t>
         </is>
       </c>
     </row>
@@ -2408,9 +2417,9 @@
           <t>Já sabe qual é o seu perfil de vinho? Responde nosso quiz e a gente te ajuda a descobrir exatamente o que combina com você. Link na bio 🍷</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Em produção</t>
         </is>
       </c>
     </row>
@@ -2430,9 +2439,9 @@
           <t>Fixamos esse post porque ele explica algo que muda como a gente trabalha com você: o quiz de perfil de vinho. Responde, descobre seu perfil e recebe o Mapa do Vinho de graça. Link na bio.</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Em produção</t>
         </is>
       </c>
     </row>

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -117,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -150,6 +150,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2329,9 +2332,9 @@
           <t>"Você sabe qual é o seu perfil de vinho?" / "A gente te ajuda a descobrir."</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
-        <is>
-          <t>Em produção</t>
+      <c r="D2" s="12" t="inlineStr">
+        <is>
+          <t>Pronto</t>
         </is>
       </c>
     </row>
@@ -2351,9 +2354,9 @@
           <t>Perguntas rápidas, respondidas em 2 minutos. A gente entende o que você já bebe, o que gosta e o que ainda não experimentou.</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>Em produção</t>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>Pronto</t>
         </is>
       </c>
     </row>
@@ -2373,9 +2376,9 @@
           <t>O resultado vem com esse guia: seu perfil e sugestões pensadas pra você. Numa linguagem simples, sem forçar a venda.</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>Em produção</t>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>Pronto</t>
         </is>
       </c>
     </row>
@@ -2395,9 +2398,9 @@
           <t>A partir daí, toda sugestão que você recebe da comnéctar já é pensada pro seu perfil. Chega de indicação genérica.</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Em produção</t>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>Pronto</t>
         </is>
       </c>
     </row>
@@ -2417,9 +2420,9 @@
           <t>Já sabe qual é o seu perfil de vinho? Responde nosso quiz e a gente te ajuda a descobrir exatamente o que combina com você. Link na bio 🍷</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>Em produção</t>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Pronto</t>
         </is>
       </c>
     </row>
@@ -2439,9 +2442,9 @@
           <t>Fixamos esse post porque ele explica algo que muda como a gente trabalha com você: o quiz de perfil de vinho. Responde, descobre seu perfil e recebe o Mapa do Vinho de graça. Link na bio.</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>Em produção</t>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Pronto</t>
         </is>
       </c>
     </row>

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -117,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -154,6 +154,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -599,17 +602,21 @@
           <t>Lançamento do novo posicionamento (dia D)</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>Em produção</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>pendente-de-criar</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
+          <t>2026-09-29-novo-posicionamento</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Aguardando 4 imagens de fundo</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="34" customHeight="1">
       <c r="A3" s="2" t="n">

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -117,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -156,6 +156,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -602,9 +605,9 @@
           <t>Lançamento do novo posicionamento (dia D)</t>
         </is>
       </c>
-      <c r="F2" s="13" t="inlineStr">
-        <is>
-          <t>Em produção</t>
+      <c r="F2" s="14" t="inlineStr">
+        <is>
+          <t>Pronto</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -614,7 +617,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Aguardando 4 imagens de fundo</t>
+          <t>Aguardando aprovação do Marcelo</t>
         </is>
       </c>
     </row>

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -35,7 +35,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -90,6 +90,12 @@
         <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B6D7A8"/>
+        <bgColor rgb="00B6D7A8"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -117,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -159,6 +165,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -526,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2278,6 +2287,48 @@
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49" ht="34" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>EXTRA</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Educação</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Calcário no vinho (bônus, fora da sequência do quiz, newsjacking educativo)</t>
+        </is>
+      </c>
+      <c r="F49" s="15" t="inlineStr">
+        <is>
+          <t>Publicado</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28-calcario-no-vinho</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Confirmado pelo Marcelo em 30/09 — publicado no Instagram via Post for Me</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -535,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -545,7 +545,7 @@
     <col width="46" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -596,12 +596,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Lançamento do novo posicionamento (dia D)</t>
+          <t>Lançamento do novo posicionamento [JÁ PRONTO: 2026-09-29-novo-posicionamento]</t>
         </is>
       </c>
       <c r="F2" s="14" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Aguardando aprovação do Marcelo</t>
+          <t>Lançamento — aguardando publicação em 01/10</t>
         </is>
       </c>
     </row>
@@ -636,12 +636,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sábado</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -672,12 +672,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Sábado</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -723,20 +723,24 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Como ler um rótulo</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+          <t>Como ler um rótulo italiano [JÁ PRONTO: 2026-09-29-rotulo-italiano]</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>Pronto</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>pendente-de-criar</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
+          <t>2026-09-29-rotulo-italiano</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Já renderizado — aguardando publicação em 07/10</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="A6" s="2" t="n">
@@ -744,12 +748,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -780,12 +784,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Domingo</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -816,12 +820,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Domingo</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -852,12 +856,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -888,12 +892,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>17/10/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sábado</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -924,12 +928,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>17/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Sábado</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -960,12 +964,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -996,12 +1000,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -1032,12 +1036,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>25/10/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Domingo</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -1068,12 +1072,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>25/10/2026</t>
+          <t>27/10/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Domingo</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -1104,12 +1108,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>27/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -1140,12 +1144,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>29/10/2026</t>
+          <t>31/10/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sábado</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
@@ -1176,12 +1180,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>31/10/2026</t>
+          <t>02/11/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Sábado</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
@@ -1212,12 +1216,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>02/11/2026</t>
+          <t>04/11/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -1248,12 +1252,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>04/11/2026</t>
+          <t>06/11/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1284,12 +1288,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>06/11/2026</t>
+          <t>08/11/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Domingo</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -1320,12 +1324,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026</t>
+          <t>10/11/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Domingo</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1356,12 +1360,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>10/11/2026</t>
+          <t>12/11/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -1392,12 +1396,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>12/11/2026</t>
+          <t>14/11/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sábado</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -1428,12 +1432,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>14/11/2026</t>
+          <t>16/11/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Sábado</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -1464,22 +1468,22 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>16/11/2026</t>
+          <t>18/11/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Segunda</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Educação</t>
+          <t>Quarta</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Bastidores</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>O que é "vinho novo"</t>
+          <t>Vinho jovem x vinho de guarda (véspera do Beaujolais, 19/11)</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -1500,22 +1504,22 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>18/11/2026</t>
+          <t>20/11/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Quarta</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>Bastidores</t>
+          <t>Sexta</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Educação</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Vinho jovem x vinho de guarda (véspera do Beaujolais, 19/11)</t>
+          <t>O que é "vinho novo" (a tradição do Beaujolais Nouveau)</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -1536,12 +1540,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>20/11/2026</t>
+          <t>22/11/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Domingo</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -1551,7 +1555,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>O que estamos provando — um vinho jovem da casa</t>
+          <t>O que estamos provando — vinho jovem da casa</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -1572,22 +1576,22 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>22/11/2026</t>
+          <t>24/11/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Domingo</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>Lifestyle</t>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Oferta</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Vinho e chocolate</t>
+          <t>Aquecimento — Black Friday chegando</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -1608,22 +1612,22 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>24/11/2026</t>
+          <t>26/11/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>Oferta</t>
+          <t>Quinta</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Bastidores</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Aquecimento — Black Friday chegando</t>
+          <t>Como montamos a seleção de Black Friday</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -1644,22 +1648,22 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>26/11/2026</t>
+          <t>28/11/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Quinta</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>Bastidores</t>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Oferta</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Como montamos a seleção de Black Friday</t>
+          <t>Últimas horas de Black Friday</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1675,29 +1679,27 @@
       <c r="H31" s="2" t="inlineStr"/>
     </row>
     <row r="32" ht="34" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>EXTRA</t>
-        </is>
+      <c r="A32" s="2" t="n">
+        <v>31</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>27/11/2026</t>
+          <t>30/11/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Sexta</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>Oferta</t>
+          <t>Segunda</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Black Friday no ar (exceção — fora do dia sim/dia não, data fixa de venda)</t>
+          <t>Vinho e chocolate</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -1714,26 +1716,26 @@
     </row>
     <row r="33" ht="34" customHeight="1">
       <c r="A33" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>28/11/2026</t>
+          <t>02/12/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Sábado</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Oferta</t>
+          <t>Quarta</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Últimas horas de Black Friday</t>
+          <t>Retrospectiva — quiz no ar</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -1750,26 +1752,26 @@
     </row>
     <row r="34" ht="34" customHeight="1">
       <c r="A34" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>30/11/2026</t>
+          <t>04/12/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Segunda</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>Lifestyle</t>
+          <t>Sexta</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Educação</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Retrospectiva — 2 meses de quiz no ar</t>
+          <t>Erro comum ao guardar vinho em casa</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -1786,26 +1788,26 @@
     </row>
     <row r="35" ht="34" customHeight="1">
       <c r="A35" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>02/12/2026</t>
+          <t>06/12/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Quarta</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>Educação</t>
+          <t>Domingo</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Bastidores</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Erro comum ao guardar vinho em casa</t>
+          <t>Bastidor de uma seleção de fim de ano</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -1822,26 +1824,26 @@
     </row>
     <row r="36" ht="34" customHeight="1">
       <c r="A36" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>04/12/2026</t>
+          <t>08/12/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Sexta</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>Bastidores</t>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Bastidor de uma seleção de fim de ano</t>
+          <t>Vinho pra ceia — começa a temporada</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -1858,26 +1860,26 @@
     </row>
     <row r="37" ht="34" customHeight="1">
       <c r="A37" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>06/12/2026</t>
+          <t>10/12/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Domingo</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>Lifestyle</t>
+          <t>Quinta</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Educação</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Vinho pra ceia — começa a temporada</t>
+          <t>Como escolher vinho de presente</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -1894,26 +1896,26 @@
     </row>
     <row r="38" ht="34" customHeight="1">
       <c r="A38" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>08/12/2026</t>
+          <t>12/12/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Educação</t>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Como escolher vinho de presente</t>
+          <t>Kits de fim de ano</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -1930,26 +1932,26 @@
     </row>
     <row r="39" ht="34" customHeight="1">
       <c r="A39" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>10/12/2026</t>
+          <t>14/12/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Quinta</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>Lifestyle</t>
+          <t>Segunda</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>Educação</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Kits de fim de ano</t>
+          <t>Vale ou não vale: espumante nacional x importado</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -1966,26 +1968,26 @@
     </row>
     <row r="40" ht="34" customHeight="1">
       <c r="A40" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>12/12/2026</t>
+          <t>16/12/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Sábado</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Educação</t>
+          <t>Quarta</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Bastidores</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Vale ou não vale: espumante nacional x importado</t>
+          <t>Última leva de importação antes do Natal</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -2002,26 +2004,26 @@
     </row>
     <row r="41" ht="34" customHeight="1">
       <c r="A41" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>14/12/2026</t>
+          <t>18/12/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Segunda</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>Bastidores</t>
+          <t>Sexta</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Última leva de importação antes do Natal</t>
+          <t>Harmonização de ceia de Natal</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -2038,26 +2040,26 @@
     </row>
     <row r="42" ht="34" customHeight="1">
       <c r="A42" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>16/12/2026</t>
+          <t>20/12/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Quarta</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>Lifestyle</t>
+          <t>Domingo</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Educação</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Harmonização de ceia de Natal</t>
+          <t>Temperatura certa pra cada tipo no calor</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -2074,26 +2076,26 @@
     </row>
     <row r="43" ht="34" customHeight="1">
       <c r="A43" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>18/12/2026</t>
+          <t>22/12/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Sexta</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>Educação</t>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Temperatura certa pra cada tipo no calor</t>
+          <t>Verão chegando — vinhos pra estação</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -2110,26 +2112,26 @@
     </row>
     <row r="44" ht="34" customHeight="1">
       <c r="A44" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>20/12/2026</t>
+          <t>24/12/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Domingo</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>Lifestyle</t>
+          <t>Quinta</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Oferta</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Verão chegando (21/12) — vinhos pra estação</t>
+          <t>Ainda dá tempo — presente de Natal</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -2146,26 +2148,26 @@
     </row>
     <row r="45" ht="34" customHeight="1">
       <c r="A45" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>22/12/2026</t>
+          <t>26/12/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>Oferta</t>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Ainda dá tempo — presente de Natal</t>
+          <t>Véspera de Natal — brinde da comnéctar</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -2182,16 +2184,16 @@
     </row>
     <row r="46" ht="34" customHeight="1">
       <c r="A46" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>24/12/2026</t>
+          <t>28/12/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -2201,7 +2203,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Véspera de Natal — brinde da comnéctar</t>
+          <t>Entre o Natal e o Ano Novo</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -2218,26 +2220,26 @@
     </row>
     <row r="47" ht="34" customHeight="1">
       <c r="A47" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>26/12/2026</t>
+          <t>30/12/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Sábado</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>Lifestyle</t>
+          <t>Quarta</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Institucional</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Entre o Natal e o Ano Novo</t>
+          <t>Fechamento do trimestre + gancho pro que vem</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -2253,78 +2255,42 @@
       <c r="H47" s="2" t="inlineStr"/>
     </row>
     <row r="48" ht="34" customHeight="1">
-      <c r="A48" s="2" t="n">
-        <v>46</v>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>EXTRA</t>
+        </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>28/12/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Segunda</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>Institucional</t>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Educação</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Fechamento do ano + gancho pro que vem em 2027</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+          <t>Calcário no vinho (bônus, fora da sequência do quiz, newsjacking educativo)</t>
+        </is>
+      </c>
+      <c r="F48" s="15" t="inlineStr">
+        <is>
+          <t>Publicado</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>pendente-de-criar</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49" ht="34" customHeight="1">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>EXTRA</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>29/09/2026</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>Educação</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>Calcário no vinho (bônus, fora da sequência do quiz, newsjacking educativo)</t>
-        </is>
-      </c>
-      <c r="F49" s="15" t="inlineStr">
-        <is>
-          <t>Publicado</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
           <t>2026-09-28-calcario-no-vinho</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Confirmado pelo Marcelo em 30/09 — publicado no Instagram via Post for Me</t>
         </is>
@@ -2332,7 +2298,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="F2:F47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Pendente,Em produção,Pronto,Publicado"</formula1>
     </dataValidation>
   </dataValidations>

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -2359,9 +2359,9 @@
           <t>"Você sabe qual é o seu perfil de vinho?" / "A gente te ajuda a descobrir."</t>
         </is>
       </c>
-      <c r="D2" s="12" t="inlineStr">
-        <is>
-          <t>Pronto</t>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>Agendado</t>
         </is>
       </c>
     </row>
@@ -2381,9 +2381,9 @@
           <t>Perguntas rápidas, respondidas em 2 minutos. A gente entende o que você já bebe, o que gosta e o que ainda não experimentou.</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
-        <is>
-          <t>Pronto</t>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Agendado</t>
         </is>
       </c>
     </row>
@@ -2403,9 +2403,9 @@
           <t>O resultado vem com esse guia: seu perfil e sugestões pensadas pra você. Numa linguagem simples, sem forçar a venda.</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>Pronto</t>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Agendado</t>
         </is>
       </c>
     </row>
@@ -2425,9 +2425,9 @@
           <t>A partir daí, toda sugestão que você recebe da comnéctar já é pensada pro seu perfil. Chega de indicação genérica.</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>Pronto</t>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Agendado</t>
         </is>
       </c>
     </row>
@@ -2447,9 +2447,9 @@
           <t>Já sabe qual é o seu perfil de vinho? Responde nosso quiz e a gente te ajuda a descobrir exatamente o que combina com você. Link na bio 🍷</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Pronto</t>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Agendado</t>
         </is>
       </c>
     </row>
@@ -2469,9 +2469,9 @@
           <t>Fixamos esse post porque ele explica algo que muda como a gente trabalha com você: o quiz de perfil de vinho. Responde, descobre seu perfil e recebe o Mapa do Vinho de graça. Link na bio.</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>Pronto</t>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Agendado</t>
         </is>
       </c>
     </row>

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -596,12 +596,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -614,9 +614,9 @@
           <t>Lançamento do novo posicionamento [JÁ PRONTO: 2026-09-29-novo-posicionamento]</t>
         </is>
       </c>
-      <c r="F2" s="14" t="inlineStr">
-        <is>
-          <t>Pronto</t>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>Agendado</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Lançamento — aguardando publicação em 01/10</t>
+          <t>Agendado via Post for Me, 02/10 17h — ID sp_CsklpAx0pE5iSg15hbF</t>
         </is>
       </c>
     </row>

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -34,7 +34,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -98,6 +98,12 @@
         <bgColor rgb="00B6D7A8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFE2F3"/>
+        <bgColor rgb="00CFE2F3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -126,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -166,6 +172,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -601,29 +610,29 @@
           <t>Sexta</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Institucional</t>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Educação</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Lançamento do novo posicionamento [JÁ PRONTO: 2026-09-29-novo-posicionamento]</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
+          <t>Roubo de 3 mil Barolos na Conterno Fantino (newsjacking, procedência)</t>
+        </is>
+      </c>
+      <c r="F2" s="14" t="inlineStr">
         <is>
           <t>Agendado</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29-novo-posicionamento</t>
+          <t>2026-10-02-roubo-barolos</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Agendado via Post for Me, 02/10 17h — ID sp_CsklpAx0pE5iSg15hbF</t>
+          <t>Agendado via Post for Me, 02/10 17h — ID sp_flGHBMmGsmEE3eJIt7e</t>
         </is>
       </c>
     </row>
@@ -641,29 +650,29 @@
           <t>Sábado</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Educação</t>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Institucional</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Roubo de 3 mil Barolos na Conterno Fantino (newsjacking, procedência)</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
+          <t>Lançamento do novo posicionamento [JÁ PRONTO: 2026-09-29-novo-posicionamento]</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
         <is>
           <t>Agendado</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02-roubo-barolos</t>
+          <t>2026-09-29-novo-posicionamento</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Agendado via Post for Me, 03/10 17h — ID sp_flGHBMmGsmEE3eJIt7e</t>
+          <t>Agendado via Post for Me, 03/10 17h — ID sp_CsklpAx0pE5iSg15hbF</t>
         </is>
       </c>
     </row>
@@ -681,27 +690,31 @@
           <t>Segunda</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Oferta</t>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Educação</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Destaque do quiz + Mapa do Vinho na grade</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+          <t>Como ler um rótulo italiano [JÁ PRONTO: 2026-09-29-rotulo-italiano]</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>Agendado</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>pendente-de-criar</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="n"/>
+          <t>2026-09-29-rotulo-italiano</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Agendado via Post for Me, 05/10 17h — ID sp_rdt3kGU9wZMNyewDNYgVf</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -717,17 +730,17 @@
           <t>Quarta</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>Lifestyle</t>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Oferta</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Vinho pro fim de semana de primavera</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
+          <t>Destaque do quiz + Mapa do Vinho na grade</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -755,29 +768,25 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Educação</t>
+          <t>Lifestyle</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Como ler um rótulo italiano [JÁ PRONTO: 2026-09-29-rotulo-italiano]</t>
+          <t>Vinho pro fim de semana de primavera</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Agendado</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29-rotulo-italiano</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Agendado via Post for Me, 09/10 17h — ID sp_rdt3kGU9wZMNyewDNYgVf</t>
-        </is>
-      </c>
+          <t>pendente-de-criar</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n"/>
     </row>
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="2" t="n">

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -740,17 +740,21 @@
           <t>Destaque do quiz + Mapa do Vinho na grade</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Pronto</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>pendente-de-criar</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="n"/>
+          <t>2026-10-07-destaque-quiz</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Renderizado — aguardando revisão de arte antes de agendar</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="A6" s="2" t="n">
@@ -776,17 +780,21 @@
           <t>Vinho pro fim de semana de primavera</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>Pronto</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>pendente-de-criar</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="n"/>
+          <t>2026-10-09-vinho-primavera</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Renderizado — aguardando revisão de arte antes de agendar</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="2" t="n">

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -712,7 +712,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Agendado via Post for Me, 05/10 17h — ID sp_rdt3kGU9wZMNyewDNYgVf</t>
+          <t>Agendado via Post for Me, 05/10 18h — ID sp_rdt3kGU9wZMNyewDNYgVf</t>
         </is>
       </c>
     </row>

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -620,9 +620,9 @@
           <t>Roubo de 3 mil Barolos na Conterno Fantino (newsjacking, procedência)</t>
         </is>
       </c>
-      <c r="F2" s="14" t="inlineStr">
-        <is>
-          <t>Agendado</t>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>Publicado</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -660,9 +660,9 @@
           <t>Lançamento do novo posicionamento [JÁ PRONTO: 2026-09-29-novo-posicionamento]</t>
         </is>
       </c>
-      <c r="F3" s="14" t="inlineStr">
-        <is>
-          <t>Agendado</t>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>Publicado</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -700,9 +700,9 @@
           <t>Como ler um rótulo italiano [JÁ PRONTO: 2026-09-29-rotulo-italiano]</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
-        <is>
-          <t>Agendado</t>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>Publicado</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -740,9 +740,9 @@
           <t>Destaque do quiz + Mapa do Vinho na grade</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>Pronto</t>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>Agendado</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Renderizado — aguardando revisão de arte antes de agendar</t>
+          <t>Agendado via Post for Me, 07/10 17h — ID sp_ckC35Fty17139Vqs27icy</t>
         </is>
       </c>
     </row>
@@ -780,9 +780,9 @@
           <t>Vinho pro fim de semana de primavera</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>Pronto</t>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>Agendado</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Renderizado — aguardando revisão de arte antes de agendar</t>
+          <t>Agendado via Post for Me, 09/10 17h — ID sp_VKJyHcE0qX5semKEyqAE</t>
         </is>
       </c>
     </row>

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -752,7 +752,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Agendado via Post for Me, 07/10 17h — ID sp_ckC35Fty17139Vqs27icy</t>
+          <t>Agendado via Post for Me, 07/10 19h (artes atualizadas) — ID sp_ckC35Fty17139Vqs27icy</t>
         </is>
       </c>
     </row>

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -792,7 +792,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Agendado via Post for Me, 09/10 17h — ID sp_VKJyHcE0qX5semKEyqAE</t>
+          <t>Agendado via Post for Me, 09/10 17h (artes finais) — ID sp_VKJyHcE0qX5semKEyqAE</t>
         </is>
       </c>
     </row>

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -820,17 +820,21 @@
           <t>Vinho como parte do momento (dia a dia)</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Pronto</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>pendente-de-criar</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="n"/>
+          <t>2026-10-11-vinho-dia-a-dia</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Renderizado — aguardando revisão de arte antes de agendar</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="2" t="n">

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -820,9 +820,9 @@
           <t>Vinho como parte do momento (dia a dia)</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>Pronto</t>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>Agendado</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Renderizado — aguardando revisão de arte antes de agendar</t>
+          <t>Agendado via Post for Me, 11/10 17h — ID sp_cb1YcJNLHwLucJ1K4Zk8</t>
         </is>
       </c>
     </row>

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -812,29 +812,25 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Lifestyle</t>
+          <t>Bastidores</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Vinho como parte do momento (dia a dia)</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="inlineStr">
-        <is>
-          <t>Agendado</t>
+          <t>Como a comnéctar escolhe o que importa</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11-vinho-dia-a-dia</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Agendado via Post for Me, 11/10 17h — ID sp_cb1YcJNLHwLucJ1K4Zk8</t>
-        </is>
-      </c>
+          <t>pendente-de-criar</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n"/>
     </row>
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="2" t="n">
@@ -850,27 +846,31 @@
           <t>Terça</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Bastidores</t>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Como a comnéctar escolhe o que importa</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+          <t>Vinho como parte do momento (dia a dia)</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>Agendado</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>pendente-de-criar</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="n"/>
+          <t>2026-10-11-vinho-dia-a-dia</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Agendado via Post for Me, 13/10 17h — ID sp_cb1YcJNLHwLucJ1K4Zk8</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="2" t="n">

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -868,7 +868,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Agendado via Post for Me, 13/10 17h — ID sp_cb1YcJNLHwLucJ1K4Zk8</t>
+          <t>Agendado via Post for Me, 13/10 18h — ID sp_cb1YcJNLHwLucJ1K4Zk8</t>
         </is>
       </c>
     </row>

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -817,7 +817,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Como a comnéctar escolhe o que importa</t>
+          <t>Como a comnéctar escolhe o que vende</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -822,15 +822,19 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Agendado</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>pendente-de-criar</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="n"/>
+          <t>2026-10-11-como-escolhemos</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Agendado via Post for Me, 11/10 18h — ID sp_8LDA3P7f8D9PIpBoofT</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="2" t="n">
@@ -2315,6 +2319,48 @@
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Confirmado pelo Marcelo em 30/09 — publicado no Instagram via Post for Me</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>EXTRA</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Quinta</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Oferta</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Quarteto Nebbiolo (Mario Costa, Clerico, Castello di Verduno, Fontanafredda)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Agendado</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>fora-do-fluxo-claude-code</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Agendado via Post for Me, 08/10 18h — ID sp_LEuR2s5ThGhyS6R3Wi8XK — criado fora deste fluxo (painel Post for Me), adicionado ao tracker pra manter controle completo</t>
         </is>
       </c>
     </row>

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -902,15 +902,19 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Agendado</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>pendente-de-criar</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="n"/>
+          <t>2026-10-15-harmonizacao-basica</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Agendado via Post for Me, 15/10 18h — ID sp_x1CFfMLfuJ4J46jtos7A8</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="2" t="n">

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -973,7 +973,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>O custo real de importar vinho</t>
+          <t>Como a gente escolhe as importadoras parceiras</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Documentação da importação</t>
+          <t>A papelada que todo vinho precisa ter antes de entrar no catálogo</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -973,7 +973,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Como a gente escolhe as importadoras parceiras</t>
+          <t>O produtor que faz vinho há 5 gerações na mesma vinha</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>A papelada que todo vinho precisa ter antes de entrar no catálogo</t>
+          <t>Decantar ou não decantar: fizemos o teste</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -942,15 +942,19 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Agendado</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>pendente-de-criar</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="n"/>
+          <t>2026-10-17-vinho-caro-sempre-melhor</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Agendado via Post for Me, 17/10 18h — ID sp_9ZDw5RHlrd7IkBlNuXoj</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="34" customHeight="1">
       <c r="A11" s="2" t="n">

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2369,6 +2369,48 @@
       <c r="H49" t="inlineStr">
         <is>
           <t>Agendado via Post for Me, 08/10 18h — ID sp_LEuR2s5ThGhyS6R3Wi8XK — criado fora deste fluxo (painel Post for Me), adicionado ao tracker pra manter controle completo</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>EXTRA</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Quarta</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Educação</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>O maior roubo de vinho da história da Itália (newsjacking Antinori)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Agendado</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-10-14-roubo-antinori</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Agendado via Post for Me, 14/10 18h — ID sp_JQKx61xXHpGJtrPwauc</t>
         </is>
       </c>
     </row>

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -982,15 +982,19 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Agendado</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>pendente-de-criar</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="n"/>
+          <t>2026-10-19-chionetti-5-geracoes</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Agendado via Post for Me, 19/10 18h — ID sp_ZIWQsH4mXweCjJNhHaJXc</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="2" t="n">

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2415,6 +2415,48 @@
       <c r="H50" t="inlineStr">
         <is>
           <t>Agendado via Post for Me, 14/10 18h — ID sp_JQKx61xXHpGJtrPwauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>EXTRA</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Sexta</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Educação</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Rafael Nadal lança vinho próprio, El Tenista (curiosidade)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Agendado</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-10-16-nadal-vinho-el-tenista</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Agendado via Post for Me, 16/10 18h — ID sp_ux15chz9nfpPYvRQsVjQr</t>
         </is>
       </c>
     </row>

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2457,6 +2457,48 @@
       <c r="H51" t="inlineStr">
         <is>
           <t>Agendado via Post for Me, 16/10 18h — ID sp_ux15chz9nfpPYvRQsVjQr</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>EXTRA</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Quinta</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Oferta</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Lançamento Robert Mondavi (post estático, 3 garrafas)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Agendado</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-10-14-mondavi-lancamento</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Agendado via Post for Me, 15/10 12h — ID sp_C9VjOKoLYChY3E5ygb</t>
         </is>
       </c>
     </row>

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -1022,15 +1022,19 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Agendado</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>pendente-de-criar</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="n"/>
+          <t>2026-10-21-uvas-pouco-conhecidas</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Agendado via Post for Me, 21/10 18h — ID sp_yvmzaTRCqvtcqqGOtWiRc</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="2" t="n">

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2503,6 +2503,48 @@
       <c r="H52" t="inlineStr">
         <is>
           <t>Agendado via Post for Me, 15/10 12h — ID sp_C9VjOKoLYChY3E5ygb</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>EXTRA</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Oferta</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>La Piu Belle Rosé - Viña Vik (promoção de verão, post estático)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Agendado</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-10-19-la-piu-belle-rose</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Agendado via Post for Me, 20/10 18h — ID sp_RF8HrEJuYUKLJLgl5e7gV</t>
         </is>
       </c>
     </row>

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -1062,15 +1062,19 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Agendado</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>pendente-de-criar</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="n"/>
+          <t>2026-10-23-vinho-nunca-ouviu-falar</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Agendado via Post for Me, 23/10 18h — ID sp_oLl6eHQtdgXLCdSpu27 — Casa do Joa (Trás-os-Montes), pé franco pré-filoxera, 3 rótulos com 1 un. cada</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="34" customHeight="1">
       <c r="A14" s="2" t="n">

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -1097,20 +1097,24 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Vale ou não vale: tampa de rosca é pior?</t>
+          <t>Por que alguns vinhos têm tampa de rosca e outros rolha?</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Agendado</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>pendente-de-criar</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="n"/>
+          <t>2026-10-25-rolha-ou-rosca</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Agendado via Post for Me, 25/10 18h — ID sp_oN514PzKWiGvfkA1c5KYI — reframed de "vale ou não vale" pra explicativo, fotos reais (rolha c/ lacre de cera e tampa de rosca)</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="34" customHeight="1">
       <c r="A15" s="2" t="n">

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -1102,7 +1102,7 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>Agendado</t>
+          <t>Em revisão</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Agendado via Post for Me, 25/10 18h — ID sp_oN514PzKWiGvfkA1c5KYI — reframed de "vale ou não vale" pra explicativo, fotos reais (rolha c/ lacre de cera e tampa de rosca)</t>
+          <t>Agendamento cancelado (ID sp_oN514PzKWiGvfkA1c5KYI) a pedido do Marcelo pra ajustes antes de republicar</t>
         </is>
       </c>
     </row>

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -1102,7 +1102,7 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>Em revisão</t>
+          <t>Agendado</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Agendamento cancelado (ID sp_oN514PzKWiGvfkA1c5KYI) a pedido do Marcelo pra ajustes antes de republicar</t>
+          <t>Agendado via Post for Me, 25/10 18h — ID sp_XtednaccHkaudMyJqgQh8 — foto da rosca no slide 3, slide 4 vinho sólido</t>
         </is>
       </c>
     </row>

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -1137,7 +1137,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Decantar ou não decantar: fizemos o teste</t>
+          <t>Decantar ou não decantar?</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -1142,15 +1142,19 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Agendado</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>pendente-de-criar</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="n"/>
+          <t>2026-10-27-decantar-ou-nao</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Agendado via Post for Me, 27/10 18h — ID sp_TzJdM9OKMQzSb0hgbY2Za — reescrito de "fizemos o teste" (não aconteceu) pra conteúdo educativo com info checada em fonte oficial (Court of Master Sommeliers)</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="2" t="n">

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -1182,15 +1182,19 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Agendado</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>pendente-de-criar</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="n"/>
+          <t>2026-10-29-harmonizacao-inusitada</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Agendado via Post for Me, 29/10 18h — ID sp_y5rmMuw8d8TLDVXqoj1T3 — espumante+batata, tinto+hambúrguer, branco+picante, fotos reais dos 3 produtos (Cave Geisse, Mario Costa, Marius Vermentino)</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="34" customHeight="1">
       <c r="A17" s="2" t="n">

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -1217,20 +1217,24 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Histórias dos produtores (1)</t>
+          <t>Histórias dos produtores: Giuseppe Cortese (Barbaresco)</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Agendado</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>pendente-de-criar</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="n"/>
+          <t>2026-10-31-giuseppe-cortese</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Agendado via Post for Me, 31/10 18h — ID sp_tZNFeonCsorq8naZUDH4 — 7 slides, história aprofundada (fundação 1971, vinhedo Rabajà, 3ª geração)</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="34" customHeight="1">
       <c r="A18" s="2" t="n">

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -1222,7 +1222,7 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Agendado</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Agendado via Post for Me, 31/10 18h — ID sp_tZNFeonCsorq8naZUDH4 — 7 slides, história aprofundada (fundação 1971, vinhedo Rabajà, 3ª geração)</t>
+          <t>Carrossel pronto (7 slides) em conteudo/carrosseis/2026-10-31-giuseppe-cortese/ - agendamento cancelado</t>
         </is>
       </c>
     </row>

--- a/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/controle-postagens.xlsx
@@ -1222,7 +1222,7 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Agendado</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Carrossel pronto (7 slides) em conteudo/carrosseis/2026-10-31-giuseppe-cortese/ - agendamento cancelado</t>
+          <t>Agendado via Post for Me, 31/10 18h - ID sp_jlD0KGu9NQrkHvaNCR32V - 7 slides com fotos reais em todos (vinhedo, adega, uvas) + fontes aumentadas</t>
         </is>
       </c>
     </row>
